--- a/examples/HFP_template.xlsx
+++ b/examples/HFP_template.xlsx
@@ -1846,8 +1846,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1883,6 +1887,11 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>property</t>
         </is>
       </c>
     </row>

--- a/examples/HFP_template.xlsx
+++ b/examples/HFP_template.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,60 +432,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -501,10 +506,13 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -518,10 +526,13 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -535,10 +546,13 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -552,10 +566,13 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -569,10 +586,13 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -586,10 +606,13 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -603,10 +626,13 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -620,10 +646,13 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -637,10 +666,13 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -654,10 +686,13 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -671,10 +706,13 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -688,10 +726,13 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -705,10 +746,13 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -722,10 +766,13 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -739,10 +786,13 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -756,10 +806,13 @@
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -773,10 +826,13 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -790,10 +846,13 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -807,10 +866,13 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -824,10 +886,13 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -841,10 +906,13 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -858,10 +926,13 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -875,10 +946,13 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,10 +966,13 @@
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -909,10 +986,13 @@
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -926,10 +1006,13 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -943,10 +1026,13 @@
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -960,10 +1046,13 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -977,10 +1066,13 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,10 +1086,13 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1011,10 +1106,13 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1028,10 +1126,13 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1045,10 +1146,13 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,10 +1166,13 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1079,10 +1186,13 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1096,10 +1206,13 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1113,10 +1226,13 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1131,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,60 +1263,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -1216,10 +1337,13 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1233,10 +1357,13 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1250,10 +1377,13 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1267,10 +1397,13 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1284,10 +1417,13 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1301,10 +1437,13 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1318,10 +1457,13 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1335,10 +1477,13 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1352,10 +1497,13 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1369,10 +1517,13 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1386,10 +1537,13 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1403,10 +1557,13 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1420,10 +1577,13 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1437,10 +1597,13 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1454,10 +1617,13 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1471,10 +1637,13 @@
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1488,10 +1657,13 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1505,10 +1677,13 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1522,10 +1697,13 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1539,10 +1717,13 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1556,10 +1737,13 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1573,10 +1757,13 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,10 +1777,13 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1607,10 +1797,13 @@
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1624,10 +1817,13 @@
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1641,10 +1837,13 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1658,10 +1857,13 @@
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1675,10 +1877,13 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1692,10 +1897,13 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1709,10 +1917,13 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1726,10 +1937,13 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1743,10 +1957,13 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1760,10 +1977,13 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1777,10 +1997,13 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1794,10 +2017,13 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1811,10 +2037,13 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1828,10 +2057,13 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1848,10 +2080,6 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/HFP_template.xlsx
+++ b/examples/HFP_template.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,40 +457,45 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>employer ctrb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -509,10 +514,10 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -529,10 +534,10 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -549,10 +554,10 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -569,10 +574,10 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -589,10 +594,10 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -609,10 +614,10 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -629,10 +634,10 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -649,10 +654,10 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -669,10 +674,10 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -689,10 +694,10 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -709,10 +714,10 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -729,10 +734,10 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -749,10 +754,10 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -769,10 +774,10 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -789,10 +794,10 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -809,10 +814,10 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -829,10 +834,10 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -849,10 +854,10 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,10 +874,10 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -889,10 +894,10 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -909,10 +914,10 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -929,10 +934,10 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -949,10 +954,10 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -969,10 +974,10 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -989,10 +994,10 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1009,10 +1014,10 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1029,10 +1034,10 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1049,10 +1054,10 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1069,10 +1074,10 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1089,10 +1094,10 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1109,10 +1114,10 @@
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1129,10 +1134,10 @@
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1149,10 +1154,10 @@
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1169,10 +1174,10 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1189,10 +1194,10 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1209,10 +1214,10 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1229,10 +1234,10 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1247,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,40 +1293,45 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>employer ctrb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -1340,10 +1350,10 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1360,10 +1370,10 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,10 +1390,10 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1400,10 +1410,10 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1420,10 +1430,10 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1440,10 +1450,10 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1460,10 +1470,10 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1480,10 +1490,10 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1500,10 +1510,10 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1520,10 +1530,10 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1540,10 +1550,10 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1560,10 +1570,10 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1580,10 +1590,10 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1600,10 +1610,10 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1620,10 +1630,10 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1640,10 +1650,10 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1660,10 +1670,10 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1680,10 +1690,10 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1700,10 +1710,10 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1720,10 +1730,10 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1740,10 +1750,10 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1760,10 +1770,10 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1780,10 +1790,10 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1800,10 +1810,10 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1820,10 +1830,10 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1840,10 +1850,10 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1860,10 +1870,10 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1880,10 +1890,10 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1900,10 +1910,10 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1920,10 +1930,10 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1940,10 +1950,10 @@
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1960,10 +1970,10 @@
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1980,10 +1990,10 @@
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2000,10 +2010,10 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2020,10 +2030,10 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2040,10 +2050,10 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2060,10 +2070,10 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>0</v>
       </c>
     </row>
